--- a/imagingServiceRequest/ig/StructureDefinition-fr-medication-administration-sequence-extension.xlsx
+++ b/imagingServiceRequest/ig/StructureDefinition-fr-medication-administration-sequence-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T08:31:28+00:00</t>
+    <t>2026-08-06T09:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
